--- a/excel_templates/手机表.xlsx
+++ b/excel_templates/手机表.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>借出</t>
+          <t>保管中</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -617,37 +617,13 @@
           <t>2026-02-11 12:58:19</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>13986903203.0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-02-07 21:46</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>测试 - 用于功能测试</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>用户自助</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026-01-29 00:00:00</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>否</t>
@@ -712,7 +688,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -843,7 +819,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>借出</t>
+          <t>保管中</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -857,37 +833,13 @@
           <t>2026-02-11 12:58:19</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>13986903203.0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-02-10 11:19</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>测试 - 用于功能测试</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>用户自助</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-02-11 14:01:08</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>否</t>
@@ -1071,7 +1023,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>丢失</t>
+          <t>保管中</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1085,21 +1037,9 @@
           <t>2026-02-11 12:58:19</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>lan</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>13800138001.0</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-01-22 11:35</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>会议室</t>
@@ -1115,21 +1055,13 @@
           <t>用户自助</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2026-01-29 00:00:00</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2026-01-30 11:35</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
@@ -1184,7 +1116,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13800138002.0</t>
+          <t>13800138002</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1600,7 +1532,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1924,7 +1856,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3992,7 +3924,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">

--- a/excel_templates/手机表.xlsx
+++ b/excel_templates/手机表.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>保管中</t>
+          <t>借出</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -833,13 +833,33 @@
           <t>2026-02-11 12:58:19</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13986903203</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:28</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>用户自助</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:28:52</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>否</t>
@@ -848,11 +868,7 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>summer</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>

--- a/excel_templates/手机表.xlsx
+++ b/excel_templates/手机表.xlsx
@@ -814,12 +814,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>借出</t>
+          <t>保管中</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -833,33 +833,13 @@
           <t>2026-02-11 12:58:19</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>13986903203</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-02-25 09:28</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>用户自助</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-02-26 09:28:52</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>否</t>
@@ -3935,12 +3915,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>13800138001</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3961,7 +3941,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-02-11 19:49:14</t>
+          <t>2026-02-26 10:24:46</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -3972,7 +3952,11 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
